--- a/populasiPenduduk.xlsx
+++ b/populasiPenduduk.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/RegEco-PADAGIMO-SOLUSI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C08BF7C7-1699-4308-9486-D6F169AF47A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{C08BF7C7-1699-4308-9486-D6F169AF47A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D27338B-2EE7-48E7-9879-966B996507C8}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{93E3B1DD-3800-4EEF-B7BE-F2447AB29B15}"/>
   </bookViews>
@@ -21,25 +21,25 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="Chart_Sektor_name">OFFSET([2]Industri_Unggulan!$B$8,1,1,[2]g!$E$3,1)</definedName>
-    <definedName name="Chart_Sektor_x">OFFSET([2]Industri_Unggulan!$F$8,1,1,[2]g!$E$3,1)</definedName>
-    <definedName name="Chart_Sektor_y">OFFSET([2]Industri_Unggulan!$E$8,1,1,[2]g!$E$3,1)</definedName>
+    <definedName name="Chart_Sektor_name">OFFSET([1]Industri_Unggulan!$B$8,1,1,[1]g!$E$3,1)</definedName>
+    <definedName name="Chart_Sektor_x">OFFSET([1]Industri_Unggulan!$F$8,1,1,[1]g!$E$3,1)</definedName>
+    <definedName name="Chart_Sektor_y">OFFSET([1]Industri_Unggulan!$E$8,1,1,[1]g!$E$3,1)</definedName>
     <definedName name="cwww10">#REF!</definedName>
-    <definedName name="Industri">[3]K.Supply!$P$2:$P$96</definedName>
-    <definedName name="Kategori">[3]Sheet1!$U$2:$U$18</definedName>
-    <definedName name="Nama_KabKota">[3]Sheet2!$F$2:$F$40</definedName>
-    <definedName name="NamaTabel">OFFSET(INDIRECT("S3R!$"&amp;[3]S2LP!$G$2&amp;"$6"),0,0,1,[3]S2LP!$G$1)</definedName>
+    <definedName name="Industri">[2]K.Supply!$P$2:$P$96</definedName>
+    <definedName name="Kategori">[2]Sheet1!$U$2:$U$18</definedName>
+    <definedName name="Nama_KabKota">[2]Sheet2!$F$2:$F$40</definedName>
+    <definedName name="NamaTabel">OFFSET(INDIRECT("S3R!$"&amp;[2]S2LP!$G$2&amp;"$6"),0,0,1,[2]S2LP!$G$1)</definedName>
     <definedName name="NamaTabelImplisit">OFFSET(INDIRECT("S3R!$"&amp;#REF!&amp;"$6"),0,0,1,#REF!)</definedName>
-    <definedName name="Produk">[3]K.Supply!$T$2:$T$76</definedName>
-    <definedName name="Tabel">OFFSET(INDIRECT("S3R!$"&amp;[3]S2LP!$G$2&amp;"$"&amp;[3]S2LP!$H$1),0,0,1,[3]S2LP!$G$1)</definedName>
+    <definedName name="Produk">[2]K.Supply!$T$2:$T$76</definedName>
+    <definedName name="Tabel">OFFSET(INDIRECT("S3R!$"&amp;[2]S2LP!$G$2&amp;"$"&amp;[2]S2LP!$H$1),0,0,1,[2]S2LP!$G$1)</definedName>
     <definedName name="TabelImplisit">OFFSET(INDIRECT("S3R!$"&amp;#REF!&amp;"$"&amp;#REF!),0,0,1,#REF!)</definedName>
-    <definedName name="TabelKab">OFFSET(INDIRECT("S3R!$"&amp;[3]S2LP!$G$2&amp;"$"&amp;[3]S2LP!$H$2),0,0,1,[3]S2LP!$G$1)</definedName>
+    <definedName name="TabelKab">OFFSET(INDIRECT("S3R!$"&amp;[2]S2LP!$G$2&amp;"$"&amp;[2]S2LP!$H$2),0,0,1,[2]S2LP!$G$1)</definedName>
     <definedName name="TabelKabImplisit">OFFSET(INDIRECT("S3R!$"&amp;#REF!&amp;"$"&amp;#REF!),0,0,1,#REF!)</definedName>
-    <definedName name="TabelKabTotal">OFFSET(INDIRECT("S3R!$"&amp;[3]S2LP!$G$2&amp;"$170"),0,0,1,[3]S2LP!$G$1)</definedName>
+    <definedName name="TabelKabTotal">OFFSET(INDIRECT("S3R!$"&amp;[2]S2LP!$G$2&amp;"$170"),0,0,1,[2]S2LP!$G$1)</definedName>
     <definedName name="TabelKabTotalImplisit">OFFSET(INDIRECT("S3R!$"&amp;#REF!&amp;"$293"),0,0,1,#REF!)</definedName>
-    <definedName name="TabelTotal">OFFSET(INDIRECT("S3R!$"&amp;[3]S2LP!$G$2&amp;"$169"),0,0,1,[3]S2LP!$G$1)</definedName>
+    <definedName name="TabelTotal">OFFSET(INDIRECT("S3R!$"&amp;[2]S2LP!$G$2&amp;"$169"),0,0,1,[2]S2LP!$G$1)</definedName>
     <definedName name="TabelTotalImplisit">OFFSET(INDIRECT("S3R!$"&amp;#REF!&amp;"$292"),0,0,1,#REF!)</definedName>
-    <definedName name="Tahun">[3]Sheet1!$A$2:$A$18</definedName>
+    <definedName name="Tahun">[2]Sheet1!$A$2:$A$18</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -188,149 +188,6 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="IO_2024 (RAW)"/>
-      <sheetName val="Tenaga Kerja"/>
-      <sheetName val="IO-2024 (CEK)"/>
-      <sheetName val="input baris R"/>
-      <sheetName val="PDRB_Kabupaten"/>
-      <sheetName val="PDRB_Padagimo"/>
-      <sheetName val="io"/>
-      <sheetName val="DeskripsiSektor"/>
-      <sheetName val="BAU_Lahan"/>
-      <sheetName val="LAS_Lahan"/>
-      <sheetName val="LDC"/>
-      <sheetName val="SType1"/>
-      <sheetName val="SType2"/>
-      <sheetName val="Stype3"/>
-      <sheetName val="ProyeksiPopulasi"/>
-      <sheetName val="populasiPenduduk"/>
-      <sheetName val="populasiPesisir"/>
-      <sheetName val="PendudukPesisir"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14">
-        <row r="8">
-          <cell r="B8">
-            <v>1367.94</v>
-          </cell>
-          <cell r="C8">
-            <v>1384.48</v>
-          </cell>
-          <cell r="D8">
-            <v>1400.87</v>
-          </cell>
-          <cell r="E8">
-            <v>1417.15</v>
-          </cell>
-          <cell r="F8">
-            <v>1433.25</v>
-          </cell>
-          <cell r="G8">
-            <v>1449.1000000000001</v>
-          </cell>
-          <cell r="H8">
-            <v>1464.8600000000001</v>
-          </cell>
-          <cell r="I8">
-            <v>1480.33</v>
-          </cell>
-          <cell r="J8">
-            <v>1495.45</v>
-          </cell>
-          <cell r="K8">
-            <v>1510.2</v>
-          </cell>
-          <cell r="L8">
-            <v>1524.52</v>
-          </cell>
-          <cell r="M8">
-            <v>1538.47</v>
-          </cell>
-          <cell r="N8">
-            <v>1551.9699999999998</v>
-          </cell>
-          <cell r="O8">
-            <v>1565.08</v>
-          </cell>
-          <cell r="P8">
-            <v>1577.78</v>
-          </cell>
-          <cell r="Q8">
-            <v>1590.05</v>
-          </cell>
-          <cell r="R8">
-            <v>1601.9254100142714</v>
-          </cell>
-          <cell r="S8">
-            <v>1613.395842050478</v>
-          </cell>
-          <cell r="T8">
-            <v>1624.4512017414752</v>
-          </cell>
-          <cell r="U8">
-            <v>1635.0817030720114</v>
-          </cell>
-          <cell r="V8">
-            <v>1645.2778827448251</v>
-          </cell>
-          <cell r="W8">
-            <v>1655.030614156773</v>
-          </cell>
-          <cell r="X8">
-            <v>1664.3311209562307</v>
-          </cell>
-          <cell r="Y8">
-            <v>1673.1709901537024</v>
-          </cell>
-          <cell r="Z8">
-            <v>1681.5421847583343</v>
-          </cell>
-          <cell r="AA8">
-            <v>1689.4370559138652</v>
-          </cell>
-          <cell r="AB8">
-            <v>1696.8483545084507</v>
-          </cell>
-          <cell r="AC8">
-            <v>1704.8150884094762</v>
-          </cell>
-          <cell r="AD8">
-            <v>1713.3446044923946</v>
-          </cell>
-          <cell r="AE8">
-            <v>1722.4448021653222</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
       <xxl21:relativeUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
@@ -459,7 +316,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -694,8 +551,149 @@
 </externalLink>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="IO_2024 (RAW)"/>
+      <sheetName val="Tenaga Kerja"/>
+      <sheetName val="IO-2024 (CEK)"/>
+      <sheetName val="input baris R"/>
+      <sheetName val="PDRB_BPS_Kabupaten"/>
+      <sheetName val="PDRB_BPS_Padagimo"/>
+      <sheetName val="io"/>
+      <sheetName val="DeskripsiSektor"/>
+      <sheetName val="BAU_Lahan"/>
+      <sheetName val="LAS_Lahan"/>
+      <sheetName val="LDC"/>
+      <sheetName val="SType1"/>
+      <sheetName val="SType2"/>
+      <sheetName val="Stype3"/>
+      <sheetName val="Skenario Hilirisasi"/>
+      <sheetName val="ProyeksiPopulasi"/>
+      <sheetName val="populasiPenduduk"/>
+      <sheetName val="populasiPesisir"/>
+      <sheetName val="PendudukPesisir"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15">
+        <row r="8">
+          <cell r="B8">
+            <v>1367.94</v>
+          </cell>
+          <cell r="C8">
+            <v>1384.48</v>
+          </cell>
+          <cell r="D8">
+            <v>1400.87</v>
+          </cell>
+          <cell r="E8">
+            <v>1417.15</v>
+          </cell>
+          <cell r="F8">
+            <v>1433.25</v>
+          </cell>
+          <cell r="G8">
+            <v>1449.1000000000001</v>
+          </cell>
+          <cell r="H8">
+            <v>1464.8600000000001</v>
+          </cell>
+          <cell r="I8">
+            <v>1480.33</v>
+          </cell>
+          <cell r="J8">
+            <v>1495.45</v>
+          </cell>
+          <cell r="K8">
+            <v>1510.2</v>
+          </cell>
+          <cell r="L8">
+            <v>1524.52</v>
+          </cell>
+          <cell r="M8">
+            <v>1538.47</v>
+          </cell>
+          <cell r="N8">
+            <v>1551.9699999999998</v>
+          </cell>
+          <cell r="O8">
+            <v>1565.08</v>
+          </cell>
+          <cell r="P8">
+            <v>1577.78</v>
+          </cell>
+          <cell r="Q8">
+            <v>1590.05</v>
+          </cell>
+          <cell r="R8">
+            <v>1601.9254100142714</v>
+          </cell>
+          <cell r="S8">
+            <v>1613.395842050478</v>
+          </cell>
+          <cell r="T8">
+            <v>1624.4512017414752</v>
+          </cell>
+          <cell r="U8">
+            <v>1635.0817030720114</v>
+          </cell>
+          <cell r="V8">
+            <v>1645.2778827448251</v>
+          </cell>
+          <cell r="W8">
+            <v>1655.030614156773</v>
+          </cell>
+          <cell r="X8">
+            <v>1664.3311209562307</v>
+          </cell>
+          <cell r="Y8">
+            <v>1673.1709901537024</v>
+          </cell>
+          <cell r="Z8">
+            <v>1681.5421847583343</v>
+          </cell>
+          <cell r="AA8">
+            <v>1689.4370559138652</v>
+          </cell>
+          <cell r="AB8">
+            <v>1696.8483545084507</v>
+          </cell>
+          <cell r="AC8">
+            <v>1704.8150884094762</v>
+          </cell>
+          <cell r="AD8">
+            <v>1713.3446044923946</v>
+          </cell>
+          <cell r="AE8">
+            <v>1722.4448021653222</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1004,7 +1002,7 @@
         <v>2020</v>
       </c>
       <c r="B2" s="4" cm="1">
-        <f t="array" ref="B2:B31">TRANSPOSE([1]ProyeksiPopulasi!B8:AE8)*1000</f>
+        <f t="array" ref="B2:B31">TRANSPOSE([3]ProyeksiPopulasi!B8:AE8)*1000</f>
         <v>1367940</v>
       </c>
     </row>
@@ -1208,39 +1206,33 @@
         <v>1689437.0559138651</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="3">
-        <v>2046</v>
-      </c>
-      <c r="B28" s="4">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B28">
         <v>1696848.3545084507</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="3">
-        <v>2047</v>
-      </c>
-      <c r="B29" s="4">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B29">
         <v>1704815.0884094762</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="3">
-        <v>2048</v>
-      </c>
-      <c r="B30" s="4">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B30">
         <v>1713344.6044923947</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="3">
-        <v>2049</v>
-      </c>
-      <c r="B31" s="4">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B31">
         <v>1722444.8021653222</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{747e98d3-0e70-4db5-a56b-cae542e688be}" enabled="0" method="" siteId="{747e98d3-0e70-4db5-a56b-cae542e688be}" removed="1"/>
+</clbl:labelList>
 </file>